--- a/candles.xlsx
+++ b/candles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Название</t>
   </si>
@@ -31,7 +31,16 @@
     <t>Цена за все товары</t>
   </si>
   <si>
-    <t>grace-kutch</t>
+    <t>ex dolore</t>
+  </si>
+  <si>
+    <t>in ea</t>
+  </si>
+  <si>
+    <t>pariatur elit</t>
+  </si>
+  <si>
+    <t>tempor</t>
   </si>
 </sst>
 </file>
@@ -338,10 +347,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="21"/>
-    <col customWidth="true" max="2" min="2" width="14"/>
-    <col customWidth="true" max="3" min="3" width="11"/>
-    <col customWidth="true" max="4" min="4" width="14"/>
+    <col customWidth="true" max="1" min="1" width="23"/>
+    <col customWidth="true" max="2" min="2" width="21"/>
+    <col customWidth="true" max="3" min="3" width="19"/>
+    <col customWidth="true" max="4" min="4" width="21"/>
     <col customWidth="true" max="5" min="5" width="10"/>
   </cols>
   <sheetData>
@@ -367,18 +376,60 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>2417</v>
+        <v>3906443</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>794816333</v>
       </c>
       <c r="D2">
-        <v>4834</v>
+        <v>-172388913</v>
       </c>
     </row>
     <row r="3">
-      <c r="E3">
-        <v>4834</v>
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>-1690580377</v>
+      </c>
+      <c r="C3">
+        <v>467292610</v>
+      </c>
+      <c r="D3">
+        <v>-955254514</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>-379301665</v>
+      </c>
+      <c r="C4">
+        <v>-32129704</v>
+      </c>
+      <c r="D4">
+        <v>779841448</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2085002839</v>
+      </c>
+      <c r="C5">
+        <v>588432665</v>
+      </c>
+      <c r="D5">
+        <v>-2116261505</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="E6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
